--- a/business_forms/033_lease_renewal_checklist_form--business_forms.xlsx
+++ b/business_forms/033_lease_renewal_checklist_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>lease_renewal_checklist_form_fields</t>
+          <t>lease_term_start_date</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>form_fields</t>
+          <t>Lease Term Start Date</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>lease_term_start_date</t>
+          <t>lease_term_end_date</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lease_term_start_date</t>
+          <t>Lease Term End Date</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>lease_term_end_date</t>
+          <t>rent_amount</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lease_term_end_date</t>
+          <t>Rent Amount</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rent_amount</t>
+          <t>lease_term_length</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rent_amount</t>
+          <t>Lease Term Length</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lease_term_length</t>
+          <t>tenant_name</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lease_term_length</t>
+          <t>Tenant Name</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>tenant_name</t>
+          <t>move_in_date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tenant_name</t>
+          <t>Move In Date</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>move_in_date</t>
+          <t>move_out_date</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>move_in_date</t>
+          <t>Move Out Date</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>move_out_date</t>
+          <t>lease_renewal_date</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>move_out_date</t>
+          <t>Lease Renewal Date</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>lease_renewal_date</t>
+          <t>lease_renewal_status</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lease_renewal_date</t>
+          <t>Lease Renewal Status</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>lease_renewal_status</t>
+          <t>lease_status</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>lease_renewal_status</t>
+          <t>Lease Status</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>lease_status</t>
+          <t>tenant_status</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lease_status</t>
+          <t>Tenant Status</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>tenant_status</t>
+          <t>notice_period</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>tenant_status</t>
+          <t>Notice Period</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>notice_period</t>
+          <t>rent_increase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>notice_period</t>
+          <t>Rent Increase</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rent_increase</t>
+          <t>rent_type</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rent_increase</t>
+          <t>Rent Type</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rent_type</t>
+          <t>lease_document</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rent_type</t>
+          <t>Lease Document</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>lease_document</t>
+          <t>rent_increase_percentage</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>lease_document</t>
+          <t>Rent Increase Percentage</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>rent_increase_percentage</t>
+          <t>tenant_occupation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rent_increase_percentage</t>
+          <t>Tenant Occupation</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>tenant_occupation</t>
+          <t>tenant_income</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>tenant_occupation</t>
+          <t>Tenant Income</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>tenant_income</t>
+          <t>lease_document_status</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>tenant_income</t>
+          <t>Lease Document Status</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>lease_document_status</t>
+          <t>tenant_document_status</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>lease_document_status</t>
+          <t>Tenant Document Status</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,17 +975,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>tenant_document_status</t>
+          <t>notice_to_move_out_date</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>tenant_document_status</t>
+          <t>Notice to Move Out Date</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>notice_to_move_out_date</t>
+          <t>lease_renewal_date_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>notice_to_move_out_date</t>
+          <t>Lease Renewal Date 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1021,17 +1021,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>lease_renewal_date</t>
+          <t>tenant_document</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>lease_renewal_date</t>
+          <t>Tenant Document</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1044,67 +1044,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>lease_renewal_date</t>
+          <t>notice_period_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>lease_renewal_date</t>
+          <t>Notice Period 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>tenant_document</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>tenant_document</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>notice_period</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>notice_period</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1290,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1557,51 +1511,51 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>notice_period_choices</t>
+          <t>notice_period_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>notice_period_choices</t>
+          <t>notice_period_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>notice_period_choices</t>
+          <t>notice_period_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
